--- a/example/tax_report_2022_monthly_rates.xlsx
+++ b/example/tax_report_2022_monthly_rates.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -165,19 +165,19 @@
     <t>2022-12-01</t>
   </si>
   <si>
-    <t>Held for 1133 days, no taxable gains as outside of speculative period of 1 years.</t>
-  </si>
-  <si>
-    <t>FOREX not acquired (e.g. received dividend payments), thus gains not taxed.</t>
-  </si>
-  <si>
-    <t>Held for 37 days, taxable gains as shorter within speculative period of 1 years.</t>
-  </si>
-  <si>
-    <t>Held for 87 days, taxable gains as shorter within speculative period of 1 years.</t>
-  </si>
-  <si>
-    <t>Held for 70 days, taxable gains as shorter within speculative period of 1 years.</t>
+    <t>Held for 1133 days, not taxable as outside of speculative period of 1 year</t>
+  </si>
+  <si>
+    <t>FOREX not acquired (e.g. received dividend payments), thus gains are not taxable</t>
+  </si>
+  <si>
+    <t>Held for 37 days, taxable since within the speculative period of 1 year</t>
+  </si>
+  <si>
+    <t>Held for 87 days, taxable since within the speculative period of 1 year</t>
+  </si>
+  <si>
+    <t>Held for 70 days, taxable since within the speculative period of 1 year</t>
   </si>
   <si>
     <t>Date</t>
@@ -219,10 +219,10 @@
     <t>Tax Withholding (AAPL)</t>
   </si>
   <si>
-    <t>ELSTER - Anlage</t>
-  </si>
-  <si>
-    <t>ELSTER - Zeile (Suggestion!)</t>
+    <t>ELSTER – Anlage</t>
+  </si>
+  <si>
+    <t>ELSTER – Zeile</t>
   </si>
   <si>
     <t>Value</t>
@@ -252,13 +252,19 @@
     <t>Zeile 65: (Werbungskosten Sonstiges): Überweisungsgebühren auf deutsches Konto für Gehaltsbestandteil RSU/ESPP</t>
   </si>
   <si>
-    <t>Zeilen 48 - 54: Gewinn / Verlust aus Verkauf von Fremdwährungen</t>
-  </si>
-  <si>
-    <t>Zeilen 48 - 54: Veräußerungswert Fremdwährungen</t>
-  </si>
-  <si>
-    <t>Zeilen 48 - 54: Anschaffungskosten Fremdwährungen</t>
+    <t>Zeile 48: Art des Wirtschaftsguts</t>
+  </si>
+  <si>
+    <t>Zeile 50: Veräußerungspreis</t>
+  </si>
+  <si>
+    <t>Zeile 51: Anschaffungskosten</t>
+  </si>
+  <si>
+    <t>Zeile 53: Gewinn / Verlust</t>
+  </si>
+  <si>
+    <t>Fremdwährungen</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1056,7 @@
     <col min="5" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="70.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="72.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1309,7 +1315,7 @@
   </sheetData>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
+  <pageSetup paperSize="8" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;CForeign Currencies</oddHeader>
   </headerFooter>
@@ -1576,12 +1582,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="105.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1657,8 +1663,8 @@
       <c r="B7" t="s">
         <v>77</v>
       </c>
-      <c r="C7">
-        <v>-43.75</v>
+      <c r="C7" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1681,6 +1687,17 @@
       </c>
       <c r="C9">
         <v>3586.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10">
+        <v>-43.75</v>
       </c>
     </row>
   </sheetData>
